--- a/kospi200.xlsx
+++ b/kospi200.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>291,750</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>하락 23,500</t>
+          <t>하락 22,750</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-7.47%</t>
+          <t>-7.23%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11,309,209</t>
+          <t>27,055,137</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,300,799</t>
+          <t>7,961,397</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17,012,671</t>
+          <t>17,056,518</t>
         </is>
       </c>
     </row>
@@ -513,12 +513,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1,743,159</t>
+          <t>4,454,306</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4,095,649</t>
+          <t>10,533,032</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -535,32 +535,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,572,000</t>
+          <t>1,585,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>하락 185,000</t>
+          <t>하락 172,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-10.53%</t>
+          <t>-9.79%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>342,339</t>
+          <t>1,014,525</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>541,610</t>
+          <t>1,628,912</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,074,386</t>
+          <t>2,091,540</t>
         </is>
       </c>
     </row>
@@ -572,32 +572,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,975,000</t>
+          <t>1,994,000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>하락 230,000</t>
+          <t>하락 211,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-10.43%</t>
+          <t>-9.57%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>278,278</t>
+          <t>702,535</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>556,567</t>
+          <t>1,410,739</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,475,200</t>
+          <t>1,489,392</t>
         </is>
       </c>
     </row>
@@ -609,32 +609,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>467,500</t>
+          <t>492,500</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>하락 20,000</t>
+          <t>상승 5,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4.10%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>289,222</t>
+          <t>994,926</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>134,157</t>
+          <t>480,609</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>957,243</t>
+          <t>1,008,432</t>
         </is>
       </c>
     </row>
@@ -646,32 +646,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>348,500</t>
+          <t>359,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>상승 500</t>
+          <t>상승 11,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+3.16%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81,586</t>
+          <t>274,341</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28,171</t>
+          <t>97,025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>815,490</t>
+          <t>840,060</t>
         </is>
       </c>
     </row>
@@ -683,32 +683,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>366,000</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>하락 21,000</t>
+          <t>하락 13,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-5.43%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>114,608</t>
+          <t>357,468</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41,241</t>
+          <t>131,954</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>732,000</t>
+          <t>748,000</t>
         </is>
       </c>
     </row>
@@ -720,32 +720,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>406,500</t>
+          <t>414,000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>하락 27,500</t>
+          <t>하락 20,000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-6.34%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>199,360</t>
+          <t>537,968</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80,174</t>
+          <t>220,780</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>659,211</t>
+          <t>671,374</t>
         </is>
       </c>
     </row>
@@ -757,32 +757,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,389,000</t>
+          <t>1,429,000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>하락 7,000</t>
+          <t>상승 33,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9,767</t>
+          <t>49,899</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,441</t>
+          <t>70,773</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>642,981</t>
+          <t>661,498</t>
         </is>
       </c>
     </row>
@@ -794,180 +794,180 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>593,000</t>
+          <t>603,000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>하락 22,000</t>
+          <t>하락 12,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73,679</t>
+          <t>184,426</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43,350</t>
+          <t>110,116</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>622,420</t>
+          <t>632,916</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1,135,000</t>
+          <t>169,300</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>상승 44,000</t>
+          <t>상승 10,800</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+4.03%</t>
+          <t>+6.81%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>99,787</t>
+          <t>1,830,842</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>112,692</t>
+          <t>307,612</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>585,245</t>
+          <t>600,486</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>164,300</t>
+          <t>1,163,000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>상승 5,800</t>
+          <t>상승 72,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+6.60%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>517,064</t>
+          <t>281,989</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>83,720</t>
+          <t>325,436</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>582,752</t>
+          <t>599,682</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>85,600</t>
+          <t>147,700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>하락 2,900</t>
+          <t>상승 6,200</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>766,202</t>
+          <t>927,257</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65,396</t>
+          <t>133,527</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>548,320</t>
+          <t>576,640</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140,400</t>
+          <t>87,800</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>하락 700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>260,186</t>
+          <t>2,002,730</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36,299</t>
+          <t>173,726</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>548,140</t>
+          <t>562,413</t>
         </is>
       </c>
     </row>
@@ -979,32 +979,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>687,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>하락 76,000</t>
+          <t>하락 69,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-9.04%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>129,599</t>
+          <t>297,337</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88,887</t>
+          <t>206,494</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>498,094</t>
+          <t>503,169</t>
         </is>
       </c>
     </row>
@@ -1016,32 +1016,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>98,700</t>
+          <t>103,600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>상승 2,300</t>
+          <t>상승 7,200</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+2.39%</t>
+          <t>+7.47%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>356,936</t>
+          <t>1,410,004</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34,729</t>
+          <t>143,290</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>468,484</t>
+          <t>491,742</t>
         </is>
       </c>
     </row>
@@ -1053,32 +1053,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>475,000</t>
+          <t>503,000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>하락 19,000</t>
+          <t>상승 9,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>145,940</t>
+          <t>435,128</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68,265</t>
+          <t>212,094</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>430,980</t>
+          <t>456,385</t>
         </is>
       </c>
     </row>
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>173,600</t>
+          <t>179,600</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>하락 900</t>
+          <t>상승 5,100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+2.92%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>120,140</t>
+          <t>547,892</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20,658</t>
+          <t>97,614</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>403,713</t>
+          <t>417,666</t>
         </is>
       </c>
     </row>
@@ -1127,32 +1127,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>467,500</t>
+          <t>483,500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>하락 23,500</t>
+          <t>하락 7,500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>133,396</t>
+          <t>335,398</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62,335</t>
+          <t>159,940</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>376,737</t>
+          <t>389,631</t>
         </is>
       </c>
     </row>
@@ -1164,32 +1164,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>240,500</t>
+          <t>243,000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>하락 23,000</t>
+          <t>하락 20,500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-8.73%</t>
+          <t>-7.78%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>570,579</t>
+          <t>1,140,469</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>137,531</t>
+          <t>277,555</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>360,750</t>
+          <t>364,500</t>
         </is>
       </c>
     </row>
@@ -1201,106 +1201,106 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>953,000</t>
+          <t>988,000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>하락 59,000</t>
+          <t>하락 24,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48,847</t>
+          <t>203,582</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46,533</t>
+          <t>203,629</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>343,529</t>
+          <t>356,146</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>106,300</t>
+          <t>122,700</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>상승 3,000</t>
+          <t>상승 6,300</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+5.41%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1,887,256</t>
+          <t>857,364</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>206,008</t>
+          <t>103,504</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>325,717</t>
+          <t>336,649</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>118,300</t>
+          <t>107,500</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>상승 1,900</t>
+          <t>상승 4,200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+4.07%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>283,678</t>
+          <t>2,836,980</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33,055</t>
+          <t>307,792</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>324,577</t>
+          <t>329,394</t>
         </is>
       </c>
     </row>
@@ -1312,106 +1312,106 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3,473,000</t>
+          <t>3,510,000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>하락 245,000</t>
+          <t>하락 208,000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-6.59%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18,257</t>
+          <t>48,566</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>63,972</t>
+          <t>172,401</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>323,842</t>
+          <t>327,292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>194,600</t>
+          <t>197,100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>하락 2,800</t>
+          <t>상승 3,800</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>317,491</t>
+          <t>1,665,898</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61,406</t>
+          <t>319,996</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>305,303</t>
+          <t>321,046</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>185,900</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>하락 7,400</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>443,960</t>
+          <t>916,119</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>81,625</t>
+          <t>181,571</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>302,803</t>
+          <t>318,482</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1423,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>617,500</t>
+          <t>619,000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>하락 5,500</t>
+          <t>하락 4,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17,472</t>
+          <t>78,575</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10,651</t>
+          <t>48,753</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>275,698</t>
+          <t>276,368</t>
         </is>
       </c>
     </row>
@@ -1460,32 +1460,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>355,500</t>
+          <t>367,000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>하락 3,000</t>
+          <t>상승 8,500</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47,034</t>
+          <t>124,819</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16,670</t>
+          <t>45,118</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>251,598</t>
+          <t>259,737</t>
         </is>
       </c>
     </row>
@@ -1497,32 +1497,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>308,000</t>
+          <t>324,000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>하락 7,000</t>
+          <t>상승 9,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78,004</t>
+          <t>251,473</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23,812</t>
+          <t>79,071</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>244,064</t>
+          <t>256,743</t>
         </is>
       </c>
     </row>
@@ -1534,32 +1534,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,600</t>
+          <t>38,650</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>보합 0</t>
+          <t>상승 1,050</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>472,690</t>
+          <t>1,904,681</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17,501</t>
+          <t>72,833</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>241,378</t>
+          <t>248,119</t>
         </is>
       </c>
     </row>
@@ -1571,106 +1571,106 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1,437,000</t>
+          <t>1,480,000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>하락 153,000</t>
+          <t>하락 110,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-9.62%</t>
+          <t>-6.92%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21,605</t>
+          <t>54,168</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>31,468</t>
+          <t>79,943</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>232,705</t>
+          <t>239,669</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>40,300</t>
+          <t>1,093,000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>하락 3,350</t>
+          <t>하락 2,000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7.67%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>698,014</t>
+          <t>12,508</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>28,174</t>
+          <t>13,554</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>225,505</t>
+          <t>228,142</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1,069,000</t>
+          <t>40,700</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>하락 26,000</t>
+          <t>하락 2,950</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-6.76%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3,320</t>
+          <t>1,684,272</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3,536</t>
+          <t>68,484</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>223,132</t>
+          <t>227,744</t>
         </is>
       </c>
     </row>
@@ -1682,32 +1682,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>29,300</t>
+          <t>30,750</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>하락 50</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+4.77%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>373,792</t>
+          <t>1,591,477</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10,901</t>
+          <t>47,961</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>213,330</t>
+          <t>223,888</t>
         </is>
       </c>
     </row>
@@ -1719,106 +1719,106 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>191,300</t>
+          <t>200,500</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>상승 1,500</t>
+          <t>상승 10,700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>251,318</t>
+          <t>597,887</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>48,310</t>
+          <t>117,251</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>208,789</t>
+          <t>218,830</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>897,000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>하락 27,500</t>
+          <t>하락 10,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-11.16%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>359,704</t>
+          <t>195,956</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>80,845</t>
+          <t>172,387</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>208,734</t>
+          <t>212,294</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>222,500</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>하락 37,000</t>
+          <t>하락 24,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-9.74%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>79,974</t>
+          <t>1,115,853</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>68,619</t>
+          <t>248,966</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>205,904</t>
+          <t>212,070</t>
         </is>
       </c>
     </row>
@@ -1830,32 +1830,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22,650</t>
+          <t>23,400</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>하락 350</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-4.63%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1,722,142</t>
+          <t>3,819,914</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>39,370</t>
+          <t>88,309</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>199,320</t>
+          <t>205,920</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>275,500</t>
+          <t>285,500</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>하락 4,500</t>
+          <t>상승 5,500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.96%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>47,370</t>
+          <t>127,231</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12,910</t>
+          <t>35,583</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>194,482</t>
+          <t>201,541</t>
         </is>
       </c>
     </row>
@@ -1904,32 +1904,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>하락 2,600</t>
+          <t>하락 600</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>205,210</t>
+          <t>596,168</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17,602</t>
+          <t>51,825</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>184,719</t>
+          <t>189,015</t>
         </is>
       </c>
     </row>
@@ -1941,106 +1941,106 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18,700</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>상승 40</t>
+          <t>상승 840</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>272,939</t>
+          <t>1,093,927</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5,064</t>
+          <t>20,956</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>176,386</t>
+          <t>183,931</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>169,500</t>
+          <t>108,300</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>상승 2,400</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>38,942</t>
+          <t>238,131</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6,549</t>
+          <t>25,570</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>175,959</t>
+          <t>181,237</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>105,000</t>
+          <t>174,400</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>하락 1,900</t>
+          <t>상승 7,300</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>58,533</t>
+          <t>187,984</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6,206</t>
+          <t>32,471</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>175,715</t>
+          <t>181,045</t>
         </is>
       </c>
     </row>
@@ -2052,106 +2052,106 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>743,000</t>
+          <t>771,000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>하락 27,000</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-3.51%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33,649</t>
+          <t>105,083</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25,647</t>
+          <t>80,416</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>163,460</t>
+          <t>169,620</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20,300</t>
+          <t>211,500</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>278,562</t>
+          <t>124,426</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5,603</t>
+          <t>25,975</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>161,877</t>
+          <t>167,070</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>201,500</t>
+          <t>20,950</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>하락 8,500</t>
+          <t>상승 700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>36,299</t>
+          <t>928,070</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7,290</t>
+          <t>19,145</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>159,171</t>
+          <t>167,061</t>
         </is>
       </c>
     </row>
@@ -2163,32 +2163,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>93,900</t>
+          <t>96,100</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>하락 4,100</t>
+          <t>하락 1,900</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>84,390</t>
+          <t>301,307</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7,920</t>
+          <t>28,618</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>158,741</t>
+          <t>162,460</t>
         </is>
       </c>
     </row>
@@ -2200,106 +2200,106 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>204,000</t>
+          <t>208,000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>상승 6,600</t>
+          <t>상승 10,600</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>+5.37%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>301,733</t>
+          <t>579,582</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62,350</t>
+          <t>120,320</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>157,851</t>
+          <t>160,946</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>409,500</t>
+          <t>36,150</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>상승 1,500</t>
+          <t>상승 1,350</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+3.88%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>151,715</t>
+          <t>1,760,066</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62,817</t>
+          <t>62,193</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>153,309</t>
+          <t>160,132</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>34,500</t>
+          <t>412,000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>하락 300</t>
+          <t>상승 4,000</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>509,320</t>
+          <t>418,862</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17,381</t>
+          <t>175,985</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>152,823</t>
+          <t>154,245</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>154,400</t>
+          <t>158,500</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 4,300</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>112,193</t>
+          <t>368,798</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17,328</t>
+          <t>57,924</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>150,502</t>
+          <t>154,498</t>
         </is>
       </c>
     </row>
@@ -2348,180 +2348,180 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>95,400</t>
+          <t>101,000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>하락 1,200</t>
+          <t>상승 4,400</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+4.55%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>99,475</t>
+          <t>349,975</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>9,368</t>
+          <t>34,293</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>144,237</t>
+          <t>152,704</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>161,300</t>
+          <t>199,000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>하락 8,900</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>77,150</t>
+          <t>163,650</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>12,486</t>
+          <t>32,020</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>143,470</t>
+          <t>149,250</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>189,300</t>
+          <t>166,100</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>하락 8,400</t>
+          <t>하락 4,100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>43,992</t>
+          <t>238,272</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>8,378</t>
+          <t>39,054</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>141,975</t>
+          <t>147,740</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>73,300</t>
+          <t>523,000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>하락 3,700</t>
+          <t>하락 1,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>252,786</t>
+          <t>68,878</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>18,856</t>
+          <t>35,156</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>138,478</t>
+          <t>143,427</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>497,000</t>
+          <t>75,600</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>하락 27,000</t>
+          <t>하락 1,400</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-5.15%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22,697</t>
+          <t>480,448</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>11,229</t>
+          <t>36,045</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>136,297</t>
+          <t>142,823</t>
         </is>
       </c>
     </row>
@@ -2533,32 +2533,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>53,300</t>
+          <t>54,400</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>하락 400</t>
+          <t>상승 700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>+1.30%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>62,563</t>
+          <t>245,477</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>3,327</t>
+          <t>13,234</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>134,328</t>
+          <t>137,100</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>114,100</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>하락 4,900</t>
+          <t>하락 2,000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>117,626</t>
+          <t>348,169</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>13,422</t>
+          <t>40,433</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>127,057</t>
+          <t>130,286</t>
         </is>
       </c>
     </row>
@@ -2607,106 +2607,106 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>222,000</t>
+          <t>229,500</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>하락 6,000</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>41,059</t>
+          <t>162,971</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>9,078</t>
+          <t>37,028</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>123,712</t>
+          <t>127,891</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>393,000</t>
+          <t>110,600</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>하락 6,000</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>54,235</t>
+          <t>188,647</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20,817</t>
+          <t>20,634</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>122,616</t>
+          <t>124,517</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>108,600</t>
+          <t>391,500</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>하락 1,000</t>
+          <t>하락 7,500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38,725</t>
+          <t>179,237</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4,155</t>
+          <t>70,440</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>122,265</t>
+          <t>122,148</t>
         </is>
       </c>
     </row>
@@ -2718,32 +2718,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>244,500</t>
+          <t>245,500</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>하락 500</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32,332</t>
+          <t>72,889</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7,818</t>
+          <t>17,798</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>112,807</t>
+          <t>113,268</t>
         </is>
       </c>
     </row>
@@ -2755,143 +2755,143 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>28,525</t>
+          <t>29,100</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>상승 725</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>+2.61%</t>
+          <t>+4.68%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1,568,261</t>
+          <t>5,475,446</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>43,767</t>
+          <t>157,912</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>105,035</t>
+          <t>107,152</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>삼성에피스홀딩스</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>412,500</t>
+          <t>22,050</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>하락 4,500</t>
+          <t>상승 1,150</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>+5.50%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11,976</t>
+          <t>792,444</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4,906</t>
+          <t>17,208</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>102,643</t>
+          <t>105,205</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성에피스홀딩스</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28,650</t>
+          <t>423,500</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>하락 900</t>
+          <t>상승 6,500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>106,733</t>
+          <t>37,090</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>3,055</t>
+          <t>15,493</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>102,093</t>
+          <t>105,380</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21,200</t>
+          <t>28,950</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>상승 300</t>
+          <t>하락 600</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>197,156</t>
+          <t>380,966</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4,145</t>
+          <t>11,033</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>101,150</t>
+          <t>103,162</t>
         </is>
       </c>
     </row>
@@ -2903,32 +2903,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>221,000</t>
+          <t>220,000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>하락 5,000</t>
+          <t>하락 6,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18,814</t>
+          <t>72,045</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4,126</t>
+          <t>15,982</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>99,082</t>
+          <t>98,634</t>
         </is>
       </c>
     </row>
@@ -2940,32 +2940,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>108,900</t>
+          <t>110,000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>하락 3,800</t>
+          <t>하락 2,700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>80,681</t>
+          <t>272,324</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>8,705</t>
+          <t>29,917</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>97,248</t>
+          <t>98,230</t>
         </is>
       </c>
     </row>
@@ -2977,32 +2977,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>49,600</t>
+          <t>49,850</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>하락 2,100</t>
+          <t>하락 1,850</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1,248,557</t>
+          <t>2,594,271</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61,633</t>
+          <t>129,404</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>97,216</t>
+          <t>97,706</t>
         </is>
       </c>
     </row>
@@ -3014,32 +3014,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>139,300</t>
+          <t>146,400</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>상승 3,200</t>
+          <t>상승 10,300</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>29,584</t>
+          <t>153,571</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4,046</t>
+          <t>22,026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>91,242</t>
+          <t>95,893</t>
         </is>
       </c>
     </row>
@@ -3051,32 +3051,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>210,500</t>
+          <t>216,500</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>상승 6,500</t>
+          <t>상승 12,500</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>115,651</t>
+          <t>370,525</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>24,200</t>
+          <t>79,562</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>90,730</t>
+          <t>93,316</t>
         </is>
       </c>
     </row>
@@ -3088,143 +3088,143 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>50,950</t>
+          <t>52,800</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>하락 350</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+2.92%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>63,139</t>
+          <t>364,999</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>3,183</t>
+          <t>19,063</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>89,633</t>
+          <t>92,887</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1,185,000</t>
+          <t>121,900</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>상승 23,000</t>
+          <t>하락 11,000</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-8.28%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>33,725</t>
+          <t>1,152,043</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>40,537</t>
+          <t>143,800</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>89,266</t>
+          <t>89,486</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>118,300</t>
+          <t>134,100</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>하락 14,600</t>
+          <t>상승 8,900</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-10.99%</t>
+          <t>+7.11%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>352,906</t>
+          <t>132,386</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>42,903</t>
+          <t>17,394</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>86,843</t>
+          <t>89,528</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>127,000</t>
+          <t>1,173,000</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>상승 1,800</t>
+          <t>상승 11,000</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22,715</t>
+          <t>64,620</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>77,420</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>84,788</t>
+          <t>88,362</t>
         </is>
       </c>
     </row>
@@ -3236,32 +3236,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>321,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>하락 26,500</t>
+          <t>하락 18,500</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-7.63%</t>
+          <t>-5.32%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18,992</t>
+          <t>68,519</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>6,176</t>
+          <t>22,568</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>84,193</t>
+          <t>86,291</t>
         </is>
       </c>
     </row>
@@ -3273,106 +3273,106 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>63,650</t>
+          <t>67,800</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>상승 850</t>
+          <t>상승 5,000</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>+1.35%</t>
+          <t>+7.96%</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>69,021</t>
+          <t>250,740</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4,359</t>
+          <t>16,447</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>78,846</t>
+          <t>83,987</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18,860</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>하락 560</t>
+          <t>상승 4,300</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1,795,076</t>
+          <t>2,405,745</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>33,557</t>
+          <t>190,155</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>77,497</t>
+          <t>77,993</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>77,800</t>
+          <t>18,810</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>상승 1,600</t>
+          <t>하락 610</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>+2.10%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>888,496</t>
+          <t>3,928,458</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>68,211</t>
+          <t>74,166</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>75,377</t>
+          <t>77,292</t>
         </is>
       </c>
     </row>
@@ -3384,254 +3384,254 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>243,000</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>하락 17,500</t>
+          <t>하락 18,500</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>-7.07%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>145,416</t>
+          <t>321,895</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>35,210</t>
+          <t>78,840</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>74,703</t>
+          <t>74,397</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>120,100</t>
+          <t>105,100</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>상승 6,500</t>
+          <t>상승 3,400</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>+5.72%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>236,853</t>
+          <t>185,714</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>27,934</t>
+          <t>18,925</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>70,250</t>
+          <t>74,104</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>99,600</t>
+          <t>78,200</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>하락 2,100</t>
+          <t>상승 5,200</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>+7.12%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>66,763</t>
+          <t>352,131</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>6,497</t>
+          <t>26,775</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>70,226</t>
+          <t>72,644</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>734,000</t>
+          <t>121,200</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>하락 42,000</t>
+          <t>상승 7,600</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-5.41%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15,224</t>
+          <t>620,781</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>11,226</t>
+          <t>74,687</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>69,328</t>
+          <t>70,893</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>96,900</t>
+          <t>742,000</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>상승 1,900</t>
+          <t>하락 34,000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>-4.38%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>30,728</t>
+          <t>45,736</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2,932</t>
+          <t>34,005</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>68,574</t>
+          <t>70,083</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>73,400</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>50,904</t>
+          <t>92,854</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3,694</t>
+          <t>8,074</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>68,185</t>
+          <t>68,916</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>85,600</t>
+          <t>97,100</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>상승 2,100</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+2.21%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>22,241</t>
+          <t>154,137</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1,893</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>67,036</t>
+          <t>68,715</t>
         </is>
       </c>
     </row>
@@ -3643,32 +3643,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>34,400</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>하락 2,800</t>
+          <t>하락 2,400</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-7.61%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1,446,957</t>
+          <t>2,766,128</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>49,514</t>
+          <t>95,243</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>66,637</t>
+          <t>67,421</t>
         </is>
       </c>
     </row>
@@ -3680,32 +3680,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>63,900</t>
+          <t>64,600</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>31,201</t>
+          <t>137,002</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1,972</t>
+          <t>8,857</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>61,252</t>
+          <t>61,923</t>
         </is>
       </c>
     </row>
@@ -3717,32 +3717,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14,050</t>
+          <t>14,440</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>하락 100</t>
+          <t>상승 290</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>123,123</t>
+          <t>682,581</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1,729</t>
+          <t>9,743</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>59,632</t>
+          <t>61,287</t>
         </is>
       </c>
     </row>
@@ -3754,32 +3754,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>34,650</t>
+          <t>35,400</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>하락 1,450</t>
+          <t>하락 700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>909,701</t>
+          <t>2,559,349</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>30,972</t>
+          <t>90,531</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>59,561</t>
+          <t>60,850</t>
         </is>
       </c>
     </row>
@@ -3791,69 +3791,69 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>123,200</t>
+          <t>123,800</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>하락 2,400</t>
+          <t>하락 1,800</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>44,855</t>
+          <t>160,927</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>5,431</t>
+          <t>19,813</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>59,040</t>
+          <t>59,327</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>143,500</t>
+          <t>458,500</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>상승 6,800</t>
+          <t>상승 36,500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>+4.97%</t>
+          <t>+8.65%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>42,762</t>
+          <t>138,001</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>6,071</t>
+          <t>60,238</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>56,734</t>
+          <t>58,738</t>
         </is>
       </c>
     </row>
@@ -3865,328 +3865,328 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>260,500</t>
+          <t>268,500</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>상승 5,000</t>
+          <t>상승 13,000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+5.09%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>21,773</t>
+          <t>97,298</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>5,624</t>
+          <t>25,937</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>56,122</t>
+          <t>57,846</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>69,900</t>
+          <t>18,360</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>하락 600</t>
+          <t>상승 1,040</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+6.00%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>72,684</t>
+          <t>882,794</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5,029</t>
+          <t>16,001</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>55,674</t>
+          <t>56,976</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>47,850</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>상승 650</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17,712</t>
+          <t>249,490</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>17,614</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>55,438</t>
+          <t>56,550</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17,760</t>
+          <t>48,650</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>상승 440</t>
+          <t>상승 1,450</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>201,913</t>
+          <t>79,989</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3,530</t>
+          <t>3,864</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>55,114</t>
+          <t>56,365</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10,930</t>
+          <t>142,300</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>하락 220</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>+4.10%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1,143,661</t>
+          <t>150,307</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>12,376</t>
+          <t>21,560</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>54,650</t>
+          <t>56,260</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>40,400</t>
+          <t>11,220</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>하락 700</t>
+          <t>상승 70</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>47,745</t>
+          <t>3,754,622</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1,908</t>
+          <t>41,958</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>54,646</t>
+          <t>56,100</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>423,500</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>상승 1,500</t>
+          <t>상승 100</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>24,959</t>
+          <t>152,482</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>10,446</t>
+          <t>6,240</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>54,255</t>
+          <t>55,728</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>124,400</t>
+          <t>85,300</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>하락 8,800</t>
+          <t>하락 4,000</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-6.61%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>180,904</t>
+          <t>551,111</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>22,530</t>
+          <t>46,352</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>54,120</t>
+          <t>55,291</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>83,200</t>
+          <t>118,600</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>하락 6,100</t>
+          <t>하락 14,600</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-6.83%</t>
+          <t>-10.96%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>261,465</t>
+          <t>1,083,764</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>21,677</t>
+          <t>132,071</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>53,930</t>
+          <t>51,596</t>
         </is>
       </c>
     </row>
@@ -4198,143 +4198,143 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>100,500</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>하락 5,700</t>
+          <t>하락 4,200</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-5.44%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>115,379</t>
+          <t>221,181</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>11,391</t>
+          <t>22,056</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>49,102</t>
+          <t>49,846</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>JB금융지주</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>25,750</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>하락 14,000</t>
+          <t>상승 1,250</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-7.57%</t>
+          <t>+5.10%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>40,315</t>
+          <t>288,471</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>6,913</t>
+          <t>7,331</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>48,374</t>
+          <t>48,475</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>160,400</t>
+          <t>170,400</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>하락 14,600</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-7.89%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>17,563</t>
+          <t>170,676</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2,795</t>
+          <t>28,867</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>46,800</t>
+          <t>48,204</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>24,700</t>
+          <t>162,200</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>상승 200</t>
+          <t>상승 2,200</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>42,680</t>
+          <t>84,285</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1,044</t>
+          <t>13,801</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>46,499</t>
+          <t>47,325</t>
         </is>
       </c>
     </row>
@@ -4346,217 +4346,217 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>52,700</t>
+          <t>54,100</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>하락 900</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>464,986</t>
+          <t>955,168</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>25,403</t>
+          <t>51,440</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>43,977</t>
+          <t>45,145</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>231,500</t>
+          <t>107,900</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>하락 8,500</t>
+          <t>하락 2,100</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-3.54%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>89,181</t>
+          <t>231,415</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>20,914</t>
+          <t>24,869</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>43,222</t>
+          <t>43,773</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>106,400</t>
+          <t>109,900</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>하락 3,600</t>
+          <t>하락 4,000</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>86,440</t>
+          <t>77,234</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>9,264</t>
+          <t>8,470</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>43,164</t>
+          <t>42,004</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>222,000</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>하락 4,900</t>
+          <t>하락 18,000</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-4.30%</t>
+          <t>-7.50%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>31,544</t>
+          <t>217,207</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>3,449</t>
+          <t>50,263</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>41,660</t>
+          <t>41,448</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>현대백화점</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>188,600</t>
+          <t>477,500</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>하락 5,400</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>24,526</t>
+          <t>27,276</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4,617</t>
+          <t>12,820</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>40,671</t>
+          <t>41,031</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>467,000</t>
+          <t>189,700</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>하락 10,000</t>
+          <t>하락 4,300</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-2.10%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7,521</t>
+          <t>92,959</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>3,412</t>
+          <t>17,621</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>40,129</t>
+          <t>40,909</t>
         </is>
       </c>
     </row>
@@ -4568,32 +4568,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3,725</t>
+          <t>3,825</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>하락 60</t>
+          <t>상승 40</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1,738,768</t>
+          <t>5,281,703</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>6,357</t>
+          <t>19,915</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>38,228</t>
+          <t>39,255</t>
         </is>
       </c>
     </row>
@@ -4605,32 +4605,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4,350</t>
+          <t>4,465</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>하락 30</t>
+          <t>상승 85</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1,015,836</t>
+          <t>2,282,242</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>4,318</t>
+          <t>9,958</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>37,781</t>
+          <t>38,780</t>
         </is>
       </c>
     </row>
@@ -4642,32 +4642,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>28,050</t>
+          <t>28,500</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>하락 300</t>
+          <t>상승 150</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>123,511</t>
+          <t>410,406</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>3,398</t>
+          <t>11,585</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>37,432</t>
+          <t>38,032</t>
         </is>
       </c>
     </row>
@@ -4679,32 +4679,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>82,300</t>
+          <t>83,100</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>상승 8,100</t>
+          <t>상승 8,900</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+10.92%</t>
+          <t>+11.99%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>33,710</t>
+          <t>184,045</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2,689</t>
+          <t>15,443</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>36,468</t>
+          <t>36,823</t>
         </is>
       </c>
     </row>
@@ -4716,32 +4716,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>242,500</t>
+          <t>246,000</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>상승 6,500</t>
+          <t>상승 10,000</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>+4.24%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>25,345</t>
+          <t>71,780</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>6,035</t>
+          <t>17,433</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>36,316</t>
+          <t>36,840</t>
         </is>
       </c>
     </row>
@@ -4753,32 +4753,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22,450</t>
+          <t>22,600</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>하락 250</t>
+          <t>하락 100</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>152,443</t>
+          <t>415,554</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>3,380</t>
+          <t>9,352</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>34,132</t>
+          <t>34,360</t>
         </is>
       </c>
     </row>
@@ -4790,291 +4790,291 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>64,800</t>
+          <t>62,800</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>상승 3,200</t>
+          <t>상승 1,200</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+5.19%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>242,637</t>
+          <t>508,458</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>15,244</t>
+          <t>32,152</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>33,852</t>
+          <t>32,807</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>강원랜드</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>38,150</t>
+          <t>14,870</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>상승 350</t>
+          <t>상승 570</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>19,732</t>
+          <t>441,453</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>6,499</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>31,258</t>
+          <t>31,813</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>강원랜드</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14,510</t>
+          <t>38,800</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>상승 210</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>96,045</t>
+          <t>89,550</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1,378</t>
+          <t>3,451</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>31,043</t>
+          <t>31,791</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>245,000</t>
+          <t>36,350</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>상승 3,500</t>
+          <t>상승 1,950</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+5.67%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>84,432</t>
+          <t>432,907</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>21,042</t>
+          <t>15,623</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>30,587</t>
+          <t>30,988</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>36,100</t>
+          <t>279,500</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>상승 1,700</t>
+          <t>하락 24,500</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>+4.94%</t>
+          <t>-8.06%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>118,533</t>
+          <t>27,773</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4,163</t>
+          <t>7,882</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>30,775</t>
+          <t>30,781</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>277,000</t>
+          <t>80,300</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>하락 27,000</t>
+          <t>상승 2,900</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-8.88%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>9,269</t>
+          <t>83,968</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2,634</t>
+          <t>6,797</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>30,506</t>
+          <t>30,761</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>79,300</t>
+          <t>33,150</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>상승 1,900</t>
+          <t>상승 600</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>10,156</t>
+          <t>110,072</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>3,626</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>30,378</t>
+          <t>30,602</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>금호석유화학</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>32,800</t>
+          <t>118,600</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>상승 250</t>
+          <t>상승 2,200</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>37,065</t>
+          <t>70,119</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1,197</t>
+          <t>8,207</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>30,279</t>
+          <t>29,837</t>
         </is>
       </c>
     </row>
@@ -5086,365 +5086,365 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>195,900</t>
+          <t>197,800</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>상승 8,100</t>
+          <t>상승 10,000</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+5.32%</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>30,380</t>
+          <t>90,345</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>5,875</t>
+          <t>17,802</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>29,491</t>
+          <t>29,777</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>115,200</t>
+          <t>37,900</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>하락 1,200</t>
+          <t>상승 1,200</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>12,228</t>
+          <t>87,482</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1,384</t>
+          <t>3,264</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>28,981</t>
+          <t>29,735</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>36,350</t>
+          <t>40,700</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>하락 350</t>
+          <t>하락 1,200</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>19,225</t>
+          <t>423,694</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>17,036</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>28,519</t>
+          <t>28,777</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>119,700</t>
+          <t>72,400</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>상승 12,900</t>
+          <t>하락 100</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>+12.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>397,868</t>
+          <t>88,158</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>46,329</t>
+          <t>6,404</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>28,255</t>
+          <t>28,303</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>72,200</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>하락 300</t>
+          <t>하락 15,500</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-6.42%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>24,781</t>
+          <t>250,115</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1,778</t>
+          <t>60,844</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>28,225</t>
+          <t>28,215</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>39,700</t>
+          <t>73,900</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>하락 2,200</t>
+          <t>상승 1,500</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-5.25%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>183,085</t>
+          <t>50,109</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>7,249</t>
+          <t>3,714</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>28,070</t>
+          <t>28,081</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>73,500</t>
+          <t>17,400</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>상승 1,100</t>
+          <t>상승 520</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+3.08%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>8,135</t>
+          <t>427,455</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>7,414</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>27,929</t>
+          <t>27,949</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>16,950</t>
+          <t>64,900</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>상승 70</t>
+          <t>상승 500</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>69,766</t>
+          <t>80,469</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1,169</t>
+          <t>5,165</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>27,226</t>
+          <t>27,761</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>에스엘</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>63,100</t>
+          <t>58,200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>하락 1,300</t>
+          <t>하락 200</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>18,598</t>
+          <t>62,257</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1,161</t>
+          <t>3,579</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>26,991</t>
+          <t>27,033</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>에스엘</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>56,400</t>
+          <t>113,400</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>하락 2,000</t>
+          <t>상승 6,600</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>+6.18%</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16,147</t>
+          <t>1,097,062</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>129,232</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>26,197</t>
+          <t>26,768</t>
         </is>
       </c>
     </row>
@@ -5456,143 +5456,143 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4,880</t>
+          <t>5,010</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>상승 80</t>
+          <t>상승 210</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>553,077</t>
+          <t>1,924,710</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>9,497</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>26,087</t>
+          <t>26,782</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>동서</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>하락 1,800</t>
+          <t>상승 1,850</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>+7.72%</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>130,857</t>
+          <t>237,511</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>8,437</t>
+          <t>6,061</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>25,151</t>
+          <t>25,723</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>46,300</t>
+          <t>65,200</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>상승 3,200</t>
+          <t>하락 1,600</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>64,975</t>
+          <t>373,207</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2,973</t>
+          <t>24,280</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>24,582</t>
+          <t>25,228</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>동서</t>
+          <t>미스토홀딩스</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24,600</t>
+          <t>46,650</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>상승 650</t>
+          <t>상승 3,550</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>+8.24%</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>35,601</t>
+          <t>277,127</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>13,111</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>24,526</t>
+          <t>24,767</t>
         </is>
       </c>
     </row>
@@ -5604,106 +5604,106 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>23,700</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>하락 50</t>
+          <t>상승 750</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+3.16%</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>27,988</t>
+          <t>124,405</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>3,002</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23,620</t>
+          <t>24,418</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>영원무역홀딩스</t>
+          <t>한국앤컴퍼니</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>25,150</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>상승 11,800</t>
+          <t>상승 950</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>+7.02%</t>
+          <t>+3.93%</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>5,882</t>
+          <t>77,011</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1,044</t>
+          <t>1,922</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>23,317</t>
+          <t>23,876</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국앤컴퍼니</t>
+          <t>영원무역홀딩스</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>24,550</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>상승 350</t>
+          <t>상승 12,800</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+7.61%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>13,460</t>
+          <t>19,406</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>3,547</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>23,307</t>
+          <t>23,446</t>
         </is>
       </c>
     </row>
@@ -5715,32 +5715,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>83,300</t>
+          <t>84,300</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>상승 900</t>
+          <t>상승 1,900</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>27,501</t>
+          <t>85,619</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2,267</t>
+          <t>7,174</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>22,987</t>
+          <t>23,263</t>
         </is>
       </c>
     </row>
@@ -5752,69 +5752,69 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>48,700</t>
+          <t>49,350</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>상승 600</t>
+          <t>상승 1,250</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+2.60%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>253,590</t>
+          <t>1,077,839</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>11,896</t>
+          <t>52,805</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>22,868</t>
+          <t>23,173</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>65,800</t>
+          <t>38,100</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>하락 3,000</t>
+          <t>보합 0</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>78,972</t>
+          <t>80,287</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>5,255</t>
+          <t>3,016</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22,320</t>
+          <t>22,293</t>
         </is>
       </c>
     </row>
@@ -5826,254 +5826,254 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>358,000</t>
+          <t>362,000</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>상승 17,000</t>
+          <t>상승 21,000</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>14,281</t>
+          <t>41,547</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>5,029</t>
+          <t>14,982</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>21,776</t>
+          <t>22,019</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>36,700</t>
+          <t>64,900</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>하락 1,400</t>
+          <t>하락 3,900</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-3.67%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>18,316</t>
+          <t>194,529</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>12,818</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>21,473</t>
+          <t>22,015</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>18,610</t>
+          <t>31,950</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>상승 330</t>
+          <t>상승 1,300</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+4.24%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>114,911</t>
+          <t>89,964</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2,111</t>
+          <t>2,807</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21,409</t>
+          <t>21,851</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>30,750</t>
+          <t>18,700</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>상승 100</t>
+          <t>상승 420</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+2.30%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15,972</t>
+          <t>449,821</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>8,394</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>21,030</t>
+          <t>21,513</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>68,100</t>
+          <t>25,200</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>하락 3,400</t>
+          <t>상승 1,600</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-4.76%</t>
+          <t>+6.78%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>32,439</t>
+          <t>241,253</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2,209</t>
+          <t>6,034</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20,579</t>
+          <t>21,069</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>24,550</t>
+          <t>121,200</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>상승 950</t>
+          <t>상승 5,600</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>+4.03%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>41,844</t>
+          <t>60,552</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1,015</t>
+          <t>7,306</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20,526</t>
+          <t>20,948</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>118,700</t>
+          <t>68,100</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>상승 3,100</t>
+          <t>하락 3,400</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>8,993</t>
+          <t>81,469</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>5,574</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20,516</t>
+          <t>20,579</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>33,037</t>
+          <t>75,764</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1,492</t>
+          <t>3,454</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6117,74 +6117,74 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>호텔신라</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>176,700</t>
+          <t>50,700</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>상승 11,400</t>
+          <t>상승 3,600</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>+6.90%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>47,413</t>
+          <t>525,558</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>8,240</t>
+          <t>26,994</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20,055</t>
+          <t>19,899</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>호텔신라</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>47,650</t>
+          <t>169,900</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>상승 550</t>
+          <t>상승 4,600</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>44,170</t>
+          <t>107,438</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2,071</t>
+          <t>18,749</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>18,702</t>
+          <t>19,283</t>
         </is>
       </c>
     </row>
@@ -6196,32 +6196,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>44,100</t>
+          <t>44,750</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>하락 1,300</t>
+          <t>하락 650</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>180,593</t>
+          <t>548,708</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>7,858</t>
+          <t>24,491</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>18,598</t>
+          <t>18,872</t>
         </is>
       </c>
     </row>
@@ -6233,32 +6233,32 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>상승 950</t>
+          <t>상승 1,450</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+6.29%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>62,160</t>
+          <t>266,916</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1,472</t>
+          <t>6,561</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>18,350</t>
+          <t>18,732</t>
         </is>
       </c>
     </row>
@@ -6270,32 +6270,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>64,700</t>
+          <t>66,200</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>하락 1,400</t>
+          <t>상승 100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>26,930</t>
+          <t>76,755</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1,736</t>
+          <t>5,030</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>18,132</t>
+          <t>18,552</t>
         </is>
       </c>
     </row>
@@ -6307,32 +6307,32 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>59,800</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>하락 2,300</t>
+          <t>하락 1,200</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>28,498</t>
+          <t>119,344</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1,699</t>
+          <t>7,245</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>17,908</t>
+          <t>18,237</t>
         </is>
       </c>
     </row>
@@ -6344,106 +6344,106 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>63,400</t>
+          <t>64,900</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>하락 1,100</t>
+          <t>상승 400</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>34,109</t>
+          <t>97,119</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2,113</t>
+          <t>6,187</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>17,242</t>
+          <t>17,650</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>CJ대한통운</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>76,500</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>하락 1,310</t>
+          <t>상승 1,200</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-7.57%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1,886,820</t>
+          <t>55,145</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>30,663</t>
+          <t>4,219</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>17,161</t>
+          <t>17,451</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CJ대한통운</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>75,200</t>
+          <t>15,550</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>하락 100</t>
+          <t>하락 1,760</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-10.17%</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>12,050</t>
+          <t>4,215,450</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>67,192</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>17,155</t>
+          <t>16,678</t>
         </is>
       </c>
     </row>
@@ -6455,32 +6455,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>상승 700</t>
+          <t>상승 800</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+3.17%</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>20,630</t>
+          <t>69,298</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>1,796</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>16,225</t>
+          <t>16,288</t>
         </is>
       </c>
     </row>
@@ -6492,32 +6492,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>33,300</t>
+          <t>33,850</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>상승 250</t>
+          <t>상승 800</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13,398</t>
+          <t>65,442</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>2,198</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>14,699</t>
+          <t>14,942</t>
         </is>
       </c>
     </row>
@@ -6529,32 +6529,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>125,500</t>
+          <t>125,100</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>상승 7,200</t>
+          <t>상승 6,800</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>+6.09%</t>
+          <t>+5.75%</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>12,359</t>
+          <t>36,131</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1,512</t>
+          <t>4,535</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>14,541</t>
+          <t>14,495</t>
         </is>
       </c>
     </row>
@@ -6566,69 +6566,69 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>123,000</t>
+          <t>123,500</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>하락 1,000</t>
+          <t>하락 500</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>8,221</t>
+          <t>21,502</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1,004</t>
+          <t>2,647</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>14,374</t>
+          <t>14,433</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>더블유게임즈</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4,830</t>
+          <t>65,900</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>하락 230</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1,238,216</t>
+          <t>62,139</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>5,895</t>
+          <t>4,125</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>13,875</t>
+          <t>13,953</t>
         </is>
       </c>
     </row>
@@ -6640,69 +6640,69 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>26,800</t>
+          <t>26,750</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>하락 700</t>
+          <t>하락 750</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>60,327</t>
+          <t>147,658</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1,617</t>
+          <t>3,972</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>13,849</t>
+          <t>13,823</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>더블유게임즈</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>65,100</t>
+          <t>4,780</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>상승 100</t>
+          <t>하락 280</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6,049</t>
+          <t>2,328,389</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>11,145</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>13,784</t>
+          <t>13,731</t>
         </is>
       </c>
     </row>
@@ -6714,32 +6714,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>14,750</t>
+          <t>14,800</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>상승 310</t>
+          <t>상승 360</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>115,718</t>
+          <t>682,700</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1,686</t>
+          <t>10,211</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>13,663</t>
+          <t>13,709</t>
         </is>
       </c>
     </row>
@@ -6751,32 +6751,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15,940</t>
+          <t>16,190</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>하락 420</t>
+          <t>하락 170</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>28,393</t>
+          <t>83,547</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>1,342</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>13,037</t>
+          <t>13,241</t>
         </is>
       </c>
     </row>
@@ -6788,32 +6788,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>314,000</t>
+          <t>320,500</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>상승 5,500</t>
+          <t>상승 12,000</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>+1.78%</t>
+          <t>+3.89%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>4,410</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>1,408</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>12,585</t>
+          <t>12,845</t>
         </is>
       </c>
     </row>
@@ -6825,106 +6825,106 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>283,500</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>하락 4,500</t>
+          <t>하락 7,000</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>3,677</t>
+          <t>14,094</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1,031</t>
+          <t>4,028</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>12,377</t>
+          <t>12,269</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>롯데정밀화학</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>32,700</t>
+          <t>45,650</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>하락 1,750</t>
+          <t>상승 300</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-5.08%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>27,181</t>
+          <t>35,003</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1,592</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>11,727</t>
+          <t>11,778</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>롯데정밀화학</t>
+          <t>세아베스틸지주</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>32,250</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>하락 350</t>
+          <t>하락 2,200</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-6.39%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>8,398</t>
+          <t>97,595</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>3,176</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>11,610</t>
+          <t>11,566</t>
         </is>
       </c>
     </row>
@@ -6936,32 +6936,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15,040</t>
+          <t>15,150</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>상승 490</t>
+          <t>상승 600</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>62,013</t>
+          <t>179,674</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>2,702</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>10,548</t>
+          <t>10,625</t>
         </is>
       </c>
     </row>
@@ -6973,32 +6973,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>14,250</t>
+          <t>14,140</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>상승 40</t>
+          <t>하락 70</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>24,510</t>
+          <t>93,774</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>1,325</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>10,480</t>
+          <t>10,399</t>
         </is>
       </c>
     </row>
@@ -7010,69 +7010,69 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>17,590</t>
+          <t>17,680</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>상승 210</t>
+          <t>상승 300</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>12,925</t>
+          <t>57,242</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1,011</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>10,227</t>
+          <t>10,280</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>롯데칠성</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>102,850</t>
+          <t>46,550</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>상승 4,250</t>
+          <t>상승 1,000</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+2.20%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>5,981</t>
+          <t>76,903</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>3,532</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>9,543</t>
+          <t>9,755</t>
         </is>
       </c>
     </row>
@@ -7084,143 +7084,143 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>857,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>상승 12,000</t>
+          <t>상승 25,000</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+2.96%</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1,996</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1,713</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>9,542</t>
+          <t>9,687</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>45,350</t>
+          <t>68,600</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>하락 200</t>
+          <t>상승 900</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>15,598</t>
+          <t>23,805</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>1,617</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>9,503</t>
+          <t>9,469</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>101,300</t>
+          <t>101,800</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>상승 5,200</t>
+          <t>상승 3,200</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>+5.41%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>6,044</t>
+          <t>21,273</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>2,185</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>9,324</t>
+          <t>9,446</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>67,300</t>
+          <t>102,900</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>하락 400</t>
+          <t>상승 6,800</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+7.08%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5,339</t>
+          <t>16,619</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1,684</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>9,289</t>
+          <t>9,472</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>93,500</t>
+          <t>93,900</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>하락 6,600</t>
+          <t>하락 6,200</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-6.59%</t>
+          <t>-6.19%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>18,054</t>
+          <t>57,429</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1,718</t>
+          <t>5,427</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>8,371</t>
+          <t>8,406</t>
         </is>
       </c>
     </row>
@@ -7269,32 +7269,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>33,500</t>
+          <t>33,950</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>상승 400</t>
+          <t>상승 850</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>7,108</t>
+          <t>41,619</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1,405</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>7,884</t>
+          <t>7,990</t>
         </is>
       </c>
     </row>
@@ -7306,32 +7306,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>6,470</t>
+          <t>6,540</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>상승 60</t>
+          <t>상승 130</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>19,728</t>
+          <t>62,961</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>409</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>7,812</t>
+          <t>7,897</t>
         </is>
       </c>
     </row>
@@ -7343,180 +7343,180 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>66,800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>상승 600</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2,440</t>
+          <t>10,450</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>697</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>7,642</t>
+          <t>7,735</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>영풍</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>39,800</t>
+          <t>112,400</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>하락 600</t>
+          <t>하락 1,000</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2,825</t>
+          <t>8,698</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>973</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>7,327</t>
+          <t>7,306</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HS효성첨단소재</t>
+          <t>영풍</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>39,500</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>하락 3,800</t>
+          <t>하락 900</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2,697</t>
+          <t>9,183</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>364</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>7,213</t>
+          <t>7,272</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>111,000</t>
+          <t>41,900</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>하락 2,400</t>
+          <t>상승 950</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2,686</t>
+          <t>45,601</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>1,892</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>7,215</t>
+          <t>7,248</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SK케미칼</t>
+          <t>HS효성첨단소재</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>161,100</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>상승 50</t>
+          <t>하락 3,700</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>12,914</t>
+          <t>10,177</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>1,642</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>7,092</t>
+          <t>7,217</t>
         </is>
       </c>
     </row>
@@ -7528,32 +7528,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>16,030</t>
+          <t>16,130</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>상승 210</t>
+          <t>상승 310</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+1.96%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>25,293</t>
+          <t>61,008</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>980</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>6,553</t>
+          <t>6,594</t>
         </is>
       </c>
     </row>
@@ -7565,32 +7565,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>17,730</t>
+          <t>17,820</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>상승 390</t>
+          <t>상승 480</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>+2.77%</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>35,250</t>
+          <t>79,383</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>1,411</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>6,143</t>
+          <t>6,174</t>
         </is>
       </c>
     </row>
@@ -7602,32 +7602,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>119,400</t>
+          <t>122,400</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>하락 1,600</t>
+          <t>상승 1,400</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>1,995</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>5,672</t>
+          <t>5,814</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>6,177</t>
+          <t>18,333</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>353</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7676,32 +7676,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>104,400</t>
+          <t>104,600</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>하락 1,900</t>
+          <t>하락 1,700</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>5,220</t>
+          <t>5,230</t>
         </is>
       </c>
     </row>
@@ -7713,32 +7713,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>115,200</t>
+          <t>116,600</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>하락 1,300</t>
+          <t>상승 100</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>3,204</t>
+          <t>10,865</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1,247</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>4,771</t>
+          <t>4,829</t>
         </is>
       </c>
     </row>
@@ -7750,32 +7750,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10,400</t>
+          <t>10,420</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>하락 480</t>
+          <t>하락 460</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>-4.23%</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>20,024</t>
+          <t>65,943</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>689</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>3,994</t>
+          <t>4,002</t>
         </is>
       </c>
     </row>
@@ -7787,32 +7787,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>15,040</t>
+          <t>15,080</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>하락 280</t>
+          <t>하락 240</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>27,452</t>
+          <t>77,272</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>1,166</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>3,730</t>
+          <t>3,740</t>
         </is>
       </c>
     </row>
@@ -7824,32 +7824,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>168,900</t>
+          <t>172,000</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>하락 7,300</t>
+          <t>하락 4,200</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>4,474</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>765</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>3,477</t>
+          <t>3,541</t>
         </is>
       </c>
     </row>
